--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484347_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484347_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4344</v>
+        <v>2.7844</v>
       </c>
       <c r="E2" t="n">
-        <v>2.587</v>
+        <v>2.9914</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1526</v>
+        <v>-0.2071</v>
       </c>
       <c r="G2" t="n">
         <v>5.5302</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1424</v>
+        <v>-0.7924</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0289</v>
+        <v>-0.6244</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1135</v>
+        <v>-0.168</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5664</v>
+        <v>1.4537</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5003</v>
+        <v>0.1969</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0661</v>
+        <v>1.2568</v>
       </c>
       <c r="G3" t="n">
         <v>0.1464</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7753</v>
+        <v>-0.888</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0522</v>
+        <v>-0.3555</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7231</v>
+        <v>-0.5325</v>
       </c>
       <c r="V3" t="n">
         <v>1.2186</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7373</v>
+        <v>0.5606</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6642</v>
+        <v>0.6236</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0732</v>
+        <v>-0.063</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8985</v>
@@ -766,13 +766,13 @@
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1651</v>
+        <v>-0.3418</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6574</v>
+        <v>-0.698</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4923</v>
+        <v>0.3561</v>
       </c>
       <c r="V4" t="n">
         <v>1.6056</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0475</v>
+        <v>-0.4825</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8119</v>
+        <v>0.0693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7644</v>
+        <v>-0.5518</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6663</v>
+        <v>2.1698</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0072</v>
+        <v>-0.649</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6735</v>
+        <v>2.8188</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7517</v>
+        <v>2.2641</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0576</v>
+        <v>0.3888</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8093</v>
+        <v>1.8752</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0854</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0504</v>
+        <v>-1.0379</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1358</v>
+        <v>0.9435</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8369</v>
+        <v>-0.9843</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0772</v>
+        <v>-0.2414</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7597</v>
+        <v>-0.743</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5507</v>
+        <v>-0.8865</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.8865</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.8375</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.234</v>
+        <v>-0.6736</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5518</v>
+        <v>-0.1639</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1698</v>
+        <v>-0.7887</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.649</v>
+        <v>0.0205</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8188</v>
+        <v>-0.8091</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2641</v>
+        <v>-0.6536</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3888</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8752</v>
+        <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.135</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9435</v>
+        <v>-0.135</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2877</v>
+        <v>-0.0488</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5447</v>
+        <v>-0.0199</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.743</v>
+        <v>-0.0289</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0264</v>
+        <v>-0.9828</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-1.257</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1912</v>
+        <v>0.2742</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7887</v>
+        <v>0.6663</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0205</v>
+        <v>-0.0072</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8091</v>
+        <v>0.6735</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6536</v>
+        <v>0.7517</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>-0.0576</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6741</v>
+        <v>0.8093</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.135</v>
+        <v>-0.0854</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.0504</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.135</v>
+        <v>-0.1358</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2377</v>
+        <v>-0.0984</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1816</v>
+        <v>-0.3678</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0561</v>
+        <v>0.2694</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5507</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1917</v>
+        <v>-1.9817</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.771</v>
+        <v>-1.6699</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4207</v>
+        <v>-0.3118</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8364</v>
@@ -1078,13 +1078,13 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5739</v>
+        <v>-0.3639</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3318</v>
+        <v>-0.2229</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.692</v>
+        <v>-2.896</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3468</v>
+        <v>0.3062</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0388</v>
+        <v>-3.2022</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6766</v>
@@ -1156,13 +1156,13 @@
         <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2108</v>
+        <v>-0.4148</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1127</v>
+        <v>-0.1533</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.2615</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6865</v>
+        <v>-4.4819</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.026</v>
+        <v>-2.0666</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6605</v>
+        <v>-2.4154</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7448</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.805</v>
+        <v>-0.6004</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3548</v>
+        <v>-0.3954</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4502</v>
+        <v>-0.205</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9414</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1083</v>
+        <v>-6.3303</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2119</v>
+        <v>-4.7064</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8963</v>
+        <v>-1.624</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2016</v>
@@ -1312,13 +1312,13 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.102</v>
+        <v>-1.3241</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.392</v>
+        <v>-0.8864</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.71</v>
+        <v>-0.4376</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6093</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.5427</v>
+        <v>-9.846</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.2271</v>
+        <v>-8.5305</v>
       </c>
       <c r="F12" t="n">
         <v>-1.3156</v>
@@ -1390,10 +1390,10 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5117</v>
+        <v>-0.8151</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1732</v>
+        <v>-0.4766</v>
       </c>
       <c r="U12" t="n">
         <v>-0.3385</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.3428</v>
+        <v>-23.04</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.0188</v>
+        <v>-14.7166</v>
       </c>
       <c r="F13" t="n">
         <v>-8.3238</v>
@@ -1438,10 +1438,10 @@
         <v>-7.8371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6751</v>
+        <v>-0.6750999999999996</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8499</v>
+        <v>1.849900000000002</v>
       </c>
       <c r="K13" t="n">
         <v>2.517</v>
@@ -1456,7 +1456,7 @@
         <v>-10.3543</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.007699999999999818</v>
+        <v>-0.00770000000000004</v>
       </c>
       <c r="P13" t="n">
         <v>-5.860300000000001</v>
@@ -1468,13 +1468,13 @@
         <v>11.7206</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.974699999999999</v>
+        <v>-6.672</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6624</v>
+        <v>-4.3597</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3123</v>
+        <v>-2.3124</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9954</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.418</v>
+        <v>5.4363</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7128</v>
+        <v>4.0425</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7052</v>
+        <v>1.3937</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2867</v>
+        <v>3.7697</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.5577</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3044</v>
+        <v>2.212</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5017</v>
+        <v>3.1806</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3315</v>
+        <v>1.3725</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1701</v>
+        <v>1.8081</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.215</v>
+        <v>0.5891</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3492</v>
+        <v>0.1852</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1342</v>
+        <v>0.4039</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>0.854</v>
+        <v>0.194</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1127</v>
+        <v>0.1707</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9667</v>
+        <v>0.0233</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5688</v>
+        <v>5.2545</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6381</v>
+        <v>2.7128</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9307</v>
+        <v>2.5417</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7697</v>
+        <v>4.2867</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5577</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.212</v>
+        <v>3.3044</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1806</v>
+        <v>4.5017</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3725</v>
+        <v>1.3315</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8081</v>
+        <v>3.1701</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5891</v>
+        <v>-0.215</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1852</v>
+        <v>-0.3492</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4039</v>
+        <v>0.1342</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6735</v>
+        <v>0.6906</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2337</v>
+        <v>-0.1127</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4397</v>
+        <v>0.8033</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.247</v>
+        <v>3.9008</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0241</v>
+        <v>2.9229</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2229</v>
+        <v>0.9778</v>
       </c>
       <c r="G16" t="n">
         <v>2.2424</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2232</v>
+        <v>0.877</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6219</v>
+        <v>0.5208</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.3561</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1985</v>
+        <v>3.207</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8645</v>
+        <v>1.1735</v>
       </c>
       <c r="F17" t="n">
-        <v>0.334</v>
+        <v>2.0335</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7552</v>
+        <v>0.1878</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7693</v>
+        <v>0.5249</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.014</v>
+        <v>-0.3371</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1661</v>
+        <v>1.4214</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7188</v>
+        <v>1.3533</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5527</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5891</v>
+        <v>-1.2336</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0504</v>
+        <v>-0.8283</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5387</v>
+        <v>-0.4052</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>2.408</v>
+        <v>0.9726</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7886</v>
+        <v>0.245</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6194</v>
+        <v>0.7276</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3321</v>
+        <v>2.4373</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1052</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.0432</v>
+        <v>3.0706</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9824</v>
+        <v>2.9545</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0607</v>
+        <v>0.1161</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1878</v>
+        <v>0.7552</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5249</v>
+        <v>0.7693</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3371</v>
+        <v>-0.014</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4214</v>
+        <v>0.1661</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3533</v>
+        <v>0.7188</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.5527</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2336</v>
+        <v>0.5891</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8283</v>
+        <v>0.0504</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4052</v>
+        <v>0.5387</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8088</v>
+        <v>1.2801</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0539</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7549</v>
+        <v>0.4015</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4373</v>
+        <v>-0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4373</v>
+        <v>2.1052</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6862</v>
+        <v>2.2578</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8621</v>
+        <v>-0.1543</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5483</v>
+        <v>2.4121</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8484</v>
@@ -1936,13 +1936,13 @@
         <v>2.7348</v>
       </c>
       <c r="S19" t="n">
-        <v>0.077</v>
+        <v>0.6486</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9849</v>
+        <v>0.8487</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1471</v>
+        <v>1.746</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8547</v>
+        <v>-0.1468</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0018</v>
+        <v>1.8929</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6784</v>
@@ -2014,13 +2014,13 @@
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2162</v>
+        <v>0.8151</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1732</v>
+        <v>0.5346</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3894</v>
+        <v>0.2805</v>
       </c>
       <c r="V20" t="n">
         <v>1.2186</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2652</v>
+        <v>0.7514</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7721</v>
+        <v>-0.3676</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0373</v>
+        <v>1.119</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8169999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2619</v>
+        <v>0.2242</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.3823</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5249</v>
+        <v>0.6066</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0132</v>
+        <v>-0.4106</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2874</v>
+        <v>-0.7929</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3006</v>
+        <v>0.3823</v>
       </c>
       <c r="G22" t="n">
         <v>1.5092</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0863</v>
+        <v>0.6624</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5614</v>
+        <v>0.0558</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5249</v>
+        <v>0.6066</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6056</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2446</v>
+        <v>-1.8711</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1221</v>
+        <v>-4.0209</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8775</v>
+        <v>2.1499</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8952</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2367</v>
+        <v>0.6101</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5009</v>
+        <v>0.602</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2642</v>
+        <v>0.0081</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>23.3426</v>
+        <v>23.3427</v>
       </c>
       <c r="E24" t="n">
-        <v>8.323499999999999</v>
+        <v>8.323700000000002</v>
       </c>
       <c r="F24" t="n">
         <v>15.019</v>
@@ -2296,7 +2296,7 @@
         <v>7.8371</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6753000000000002</v>
+        <v>0.6752999999999993</v>
       </c>
       <c r="J24" t="n">
         <v>10.3621</v>
@@ -2305,7 +2305,7 @@
         <v>10.3542</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00790000000000024</v>
+        <v>0.007899999999999796</v>
       </c>
       <c r="M24" t="n">
         <v>-1.85</v>
@@ -2326,13 +2326,13 @@
         <v>17.5807</v>
       </c>
       <c r="S24" t="n">
-        <v>6.974799999999999</v>
+        <v>6.9747</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3125</v>
+        <v>2.3124</v>
       </c>
       <c r="U24" t="n">
-        <v>4.6625</v>
+        <v>4.6623</v>
       </c>
       <c r="V24" t="n">
         <v>1.9954</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484347_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484347_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,47 +549,52 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7844</v>
+        <v>2.1774</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9914</v>
+        <v>2.3845</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2071</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5302</v>
+        <v>4.9233</v>
       </c>
       <c r="H2" t="n">
         <v>4.3976</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1326</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3041</v>
+        <v>5.6971</v>
       </c>
       <c r="K2" t="n">
         <v>5.7099</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5942</v>
+        <v>-0.0128</v>
       </c>
       <c r="M2" t="n">
         <v>-0.7739</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,377 +729,397 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5606</v>
+        <v>0.914</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6236</v>
+        <v>0.914</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.063</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8985</v>
+        <v>0.914</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0481</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8504</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0796</v>
+        <v>0.914</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9849</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9781</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.033</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3418</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.698</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3561</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6056</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4825</v>
+        <v>0.607</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0693</v>
+        <v>0.607</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5518</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1698</v>
+        <v>0.607</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.649</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8188</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2641</v>
+        <v>0.607</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3888</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8752</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9843</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2414</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.743</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8375</v>
+        <v>-0.3534</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6736</v>
+        <v>-0.2904</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1639</v>
+        <v>-0.063</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7887</v>
+        <v>-1.8124</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0205</v>
+        <v>-0.3551</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8091</v>
+        <v>-1.4574</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6536</v>
+        <v>0.1657</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6741</v>
+        <v>-0.5122</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.135</v>
+        <v>-1.9781</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.033</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.135</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0488</v>
+        <v>-0.3418</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0199</v>
+        <v>-0.698</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0289</v>
+        <v>0.3561</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.6056</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9828</v>
+        <v>-0.4825</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.257</v>
+        <v>0.0693</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2742</v>
+        <v>-0.5518</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6663</v>
+        <v>2.1698</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0072</v>
+        <v>-0.649</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6735</v>
+        <v>2.8188</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7517</v>
+        <v>2.2641</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0576</v>
+        <v>0.3888</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8093</v>
+        <v>1.8752</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0854</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0504</v>
+        <v>-1.0379</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1358</v>
+        <v>0.9435</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0984</v>
+        <v>-0.9843</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3678</v>
+        <v>-0.2414</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2694</v>
+        <v>-0.743</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5507</v>
+        <v>-0.8865</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-0.8865</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9817</v>
+        <v>-0.8375</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6699</v>
+        <v>-0.6736</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3118</v>
+        <v>-0.1639</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8364</v>
+        <v>-0.7887</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1887</v>
+        <v>-0.8091</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5522</v>
+        <v>-0.6536</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0409</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2842</v>
+        <v>-0.135</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6887</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4045</v>
+        <v>-0.135</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3639</v>
+        <v>-0.0488</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.141</v>
+        <v>-0.0199</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2229</v>
+        <v>-0.0289</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,558 +1129,594 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.896</v>
+        <v>-0.9828</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3062</v>
+        <v>-1.257</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2022</v>
+        <v>0.2742</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6766</v>
+        <v>0.6663</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3661</v>
+        <v>-0.0072</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3105</v>
+        <v>0.6735</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2175</v>
+        <v>0.7517</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1228</v>
+        <v>-0.0576</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.8093</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8941</v>
+        <v>-0.0854</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4889</v>
+        <v>0.0504</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4052</v>
+        <v>-0.1358</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4148</v>
+        <v>-0.0984</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1533</v>
+        <v>-0.3678</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2615</v>
+        <v>0.2694</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-1.5507</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4373</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4819</v>
+        <v>-1.9817</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0666</v>
+        <v>-1.6699</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4154</v>
+        <v>-0.3118</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7448</v>
+        <v>-0.8364</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5334</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2114</v>
+        <v>-0.1887</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9717</v>
+        <v>-0.5522</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4298</v>
+        <v>0.0409</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4015</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7731</v>
+        <v>-0.2842</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.6887</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8099</v>
+        <v>0.4045</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6004</v>
+        <v>-0.3639</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3954</v>
+        <v>-0.141</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.205</v>
+        <v>-0.2229</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3303</v>
+        <v>-2.896</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7064</v>
+        <v>0.3062</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.624</v>
+        <v>-3.2022</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2016</v>
+        <v>-0.6766</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6897</v>
+        <v>-0.3661</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5118</v>
+        <v>-0.3105</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.753</v>
+        <v>0.2175</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.5122</v>
+        <v>0.1228</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2408</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4485</v>
+        <v>-0.8941</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1775</v>
+        <v>-0.4889</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.271</v>
+        <v>-0.4052</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3241</v>
+        <v>-0.4148</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8864</v>
+        <v>-0.1533</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4376</v>
+        <v>-0.2615</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8865</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4959</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.846</v>
+        <v>-4.4819</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.5305</v>
+        <v>-2.0666</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3156</v>
+        <v>-2.4154</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.8784</v>
+        <v>-2.7448</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.5944</v>
+        <v>-0.5334</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2841</v>
+        <v>-2.2114</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.1471</v>
+        <v>-0.9717</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.2685</v>
+        <v>0.4298</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1214</v>
+        <v>-1.4015</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7314</v>
+        <v>-1.7731</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.3259</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4054</v>
+        <v>-0.8099</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.5395</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8151</v>
+        <v>-0.6004</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4766</v>
+        <v>-0.3954</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3385</v>
+        <v>-0.205</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3869</v>
+        <v>-0.9414</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.04</v>
+        <v>-6.3303</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.7166</v>
+        <v>-4.7064</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.3238</v>
+        <v>-1.624</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.5123</v>
+        <v>-4.2016</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.8371</v>
+        <v>-3.6897</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6750999999999996</v>
+        <v>-0.5118</v>
       </c>
       <c r="J13" t="n">
-        <v>1.849900000000002</v>
+        <v>-2.753</v>
       </c>
       <c r="K13" t="n">
-        <v>2.517</v>
+        <v>-2.5122</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6673000000000001</v>
+        <v>-0.2408</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.3621</v>
+        <v>-1.4485</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.3543</v>
+        <v>-1.1775</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.00770000000000004</v>
+        <v>-0.271</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.860300000000001</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.5808</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>11.7206</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.672</v>
+        <v>-1.3241</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.3597</v>
+        <v>-0.8864</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3124</v>
+        <v>-0.4376</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9954</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>5.373899999999999</v>
+        <v>0.8865</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.3696</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4363</v>
+        <v>-9.846</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0425</v>
+        <v>-8.5305</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3937</v>
+        <v>-1.3156</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7697</v>
+        <v>-6.8784</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5577</v>
+        <v>-6.5944</v>
       </c>
       <c r="I14" t="n">
-        <v>2.212</v>
+        <v>-0.2841</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1806</v>
+        <v>-4.1471</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3725</v>
+        <v>-4.2685</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8081</v>
+        <v>0.1214</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5891</v>
+        <v>-2.7314</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1852</v>
+        <v>-2.3259</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4039</v>
+        <v>-0.4054</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-3.9069</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.194</v>
+        <v>-0.8151</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1707</v>
+        <v>-0.4766</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0233</v>
+        <v>-0.3385</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8865</v>
+        <v>0.3869</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2545</v>
+        <v>-23.04</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7128</v>
+        <v>-14.7165</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5417</v>
+        <v>-8.3238</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2867</v>
+        <v>-8.5121</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9824000000000001</v>
+        <v>-7.8371</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3044</v>
+        <v>-0.6749999999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5017</v>
+        <v>1.85</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3315</v>
+        <v>2.517</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1701</v>
+        <v>-0.6671999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.215</v>
+        <v>-10.3621</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3492</v>
+        <v>-10.3543</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1342</v>
+        <v>-0.00770000000000004</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-5.8603</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-17.5808</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>11.7206</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6906</v>
+        <v>-6.672</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1127</v>
+        <v>-4.3597</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8033</v>
+        <v>-2.3124</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>-1.9954</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>5.373899999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.3696</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9008</v>
+        <v>5.4363</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9229</v>
+        <v>4.0425</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9778</v>
+        <v>1.3937</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2424</v>
+        <v>3.7697</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0425</v>
+        <v>1.5577</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>2.212</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3788</v>
+        <v>3.1806</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7176</v>
+        <v>1.3725</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6613</v>
+        <v>1.8081</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8636</v>
+        <v>0.5891</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3249</v>
+        <v>0.1852</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5387</v>
+        <v>0.4039</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>0.877</v>
+        <v>0.194</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5208</v>
+        <v>0.1707</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3561</v>
+        <v>0.0233</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.207</v>
+        <v>5.2545</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1735</v>
+        <v>2.7128</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0335</v>
+        <v>2.5417</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1878</v>
+        <v>4.2867</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5249</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3371</v>
+        <v>3.3044</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4214</v>
+        <v>4.5017</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3533</v>
+        <v>1.3315</v>
       </c>
       <c r="L17" t="n">
-        <v>0.06809999999999999</v>
+        <v>3.1701</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2336</v>
+        <v>-0.215</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8283</v>
+        <v>-0.3492</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4052</v>
+        <v>0.1342</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9726</v>
+        <v>0.6906</v>
       </c>
       <c r="T17" t="n">
-        <v>0.245</v>
+        <v>-0.1127</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7276</v>
+        <v>0.8033</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0706</v>
+        <v>3.9008</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9545</v>
+        <v>2.9229</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1161</v>
+        <v>0.9778</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7552</v>
+        <v>2.2424</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7693</v>
+        <v>1.0425</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.014</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1661</v>
+        <v>1.3788</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7188</v>
+        <v>0.7176</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5527</v>
+        <v>0.6613</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5891</v>
+        <v>0.8636</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0504</v>
+        <v>0.3249</v>
       </c>
       <c r="O18" t="n">
         <v>0.5387</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2801</v>
+        <v>0.877</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.5208</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4015</v>
+        <v>0.3561</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1052</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2578</v>
+        <v>3.207</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1543</v>
+        <v>1.1735</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4121</v>
+        <v>2.0335</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8484</v>
+        <v>0.1878</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.5249</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9435</v>
+        <v>-0.3371</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0457</v>
+        <v>1.4214</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7188</v>
+        <v>1.3533</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6731</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8941</v>
+        <v>-1.2336</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6237</v>
+        <v>-0.8283</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2704</v>
+        <v>-0.4052</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7348</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6486</v>
+        <v>0.9726</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2</v>
+        <v>0.245</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8487</v>
+        <v>0.7276</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.746</v>
+        <v>3.0706</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1468</v>
+        <v>2.9545</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8929</v>
+        <v>0.1161</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6784</v>
+        <v>0.7552</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7626</v>
+        <v>0.7693</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.441</v>
+        <v>-0.014</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.728</v>
+        <v>0.1661</v>
       </c>
       <c r="K20" t="n">
-        <v>1.847</v>
+        <v>0.7188</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.575</v>
+        <v>-0.5527</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0496</v>
+        <v>0.5891</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0844</v>
+        <v>0.0504</v>
       </c>
       <c r="O20" t="n">
-        <v>0.134</v>
+        <v>0.5387</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8151</v>
+        <v>1.2801</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5346</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2805</v>
+        <v>0.4015</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>2.1052</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7514</v>
+        <v>2.2578</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3676</v>
+        <v>-0.1543</v>
       </c>
       <c r="F21" t="n">
-        <v>1.119</v>
+        <v>2.4121</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.8484</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1433</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6737</v>
+        <v>-0.9435</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2625</v>
+        <v>0.0457</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4106</v>
+        <v>0.7188</v>
       </c>
       <c r="L21" t="n">
         <v>-0.6731</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5544</v>
+        <v>-0.8941</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5538</v>
+        <v>-0.6237</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.2704</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2242</v>
+        <v>0.6486</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3823</v>
+        <v>-0.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6066</v>
+        <v>0.8487</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4106</v>
+        <v>1.746</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7929</v>
+        <v>-0.1468</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3823</v>
+        <v>1.8929</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5092</v>
+        <v>-0.6784</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7792</v>
+        <v>1.7626</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.27</v>
+        <v>-2.441</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4683</v>
+        <v>-0.728</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3331</v>
+        <v>1.847</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1352</v>
+        <v>-2.575</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9591</v>
+        <v>0.0496</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5538</v>
+        <v>-0.0844</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4052</v>
+        <v>0.134</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6624</v>
+        <v>0.8151</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0558</v>
+        <v>0.5346</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6066</v>
+        <v>0.2805</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6056</v>
+        <v>1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3869</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8711</v>
+        <v>0.7514</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0209</v>
+        <v>-0.3676</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1499</v>
+        <v>1.119</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8952</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5334</v>
+        <v>-0.1433</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3618</v>
+        <v>-0.6737</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.81</v>
+        <v>-0.2625</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.449</v>
+        <v>0.4106</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.361</v>
+        <v>-0.6731</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0852</v>
+        <v>-0.5544</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0844</v>
+        <v>-0.5538</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0008</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6101</v>
+        <v>0.2242</v>
       </c>
       <c r="T23" t="n">
-        <v>0.602</v>
+        <v>-0.3823</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0081</v>
+        <v>0.6066</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6642</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-0.4106</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.7929</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.5092</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.7792</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.4683</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.3331</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.9591</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5538</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.4052</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.6056</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. REYES QUEZADA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.8711</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.0209</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.1499</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.8952</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.5334</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.3618</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.449</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.361</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.0852</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484347_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>23.3427</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>8.323700000000002</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>15.019</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>8.512</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>7.8371</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>0.6752999999999993</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>10.3621</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K26" t="n">
         <v>10.3542</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>0.007899999999999796</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-1.85</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-2.5171</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>0.6672999999999999</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>5.8603</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>17.5807</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>6.9747</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>2.3124</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>4.6623</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>1.9954</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>7.369499999999999</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-5.374</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
